--- a/4.evidence/PLC-S/SAP_VA05_SalesOrderList_FY2025.xlsx
+++ b/4.evidence/PLC-S/SAP_VA05_SalesOrderList_FY2025.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -62,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -84,11 +83,55 @@
         <color rgb="00888888"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,6 +155,8 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N177"/>
+  <dimension ref="A1:O177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -494,6 +539,7 @@
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,6 +627,11 @@
           <t>出荷予定日</t>
         </is>
       </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>顧客PO番号</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -645,6 +696,11 @@
       <c r="N5" s="8" t="n">
         <v>45769</v>
       </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08630</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -709,6 +765,11 @@
       <c r="N6" s="8" t="n">
         <v>45763</v>
       </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01073</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -773,6 +834,11 @@
       <c r="N7" s="8" t="n">
         <v>45788</v>
       </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10808</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -837,6 +903,11 @@
       <c r="N8" s="8" t="n">
         <v>45789</v>
       </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10016</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -901,6 +972,11 @@
       <c r="N9" s="8" t="n">
         <v>45778</v>
       </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -965,6 +1041,11 @@
       <c r="N10" s="8" t="n">
         <v>45794</v>
       </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01438</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1029,6 +1110,11 @@
       <c r="N11" s="8" t="n">
         <v>45772</v>
       </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08762</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1093,6 +1179,11 @@
       <c r="N12" s="8" t="n">
         <v>45791</v>
       </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12854</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1157,6 +1248,11 @@
       <c r="N13" s="8" t="n">
         <v>45795</v>
       </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13778</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1221,6 +1317,11 @@
       <c r="N14" s="8" t="n">
         <v>45782</v>
       </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06320</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1285,6 +1386,11 @@
       <c r="N15" s="8" t="n">
         <v>45783</v>
       </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12722</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1349,6 +1455,11 @@
       <c r="N16" s="8" t="n">
         <v>45791</v>
       </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12062</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1413,6 +1524,11 @@
       <c r="N17" s="8" t="n">
         <v>45786</v>
       </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01146</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1477,6 +1593,11 @@
       <c r="N18" s="8" t="n">
         <v>45792</v>
       </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05462</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1541,6 +1662,11 @@
       <c r="N19" s="8" t="n">
         <v>45787</v>
       </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01219</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1605,6 +1731,11 @@
       <c r="N20" s="8" t="n">
         <v>45818</v>
       </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07772</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1669,6 +1800,11 @@
       <c r="N21" s="8" t="n">
         <v>45811</v>
       </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07970</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1733,6 +1869,11 @@
       <c r="N22" s="8" t="n">
         <v>45827</v>
       </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09818</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1797,6 +1938,11 @@
       <c r="N23" s="8" t="n">
         <v>45798</v>
       </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01292</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1861,6 +2007,11 @@
       <c r="N24" s="8" t="n">
         <v>45819</v>
       </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06518</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1925,6 +2076,11 @@
       <c r="N25" s="8" t="n">
         <v>45827</v>
       </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08894</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1989,6 +2145,11 @@
       <c r="N26" s="8" t="n">
         <v>45820</v>
       </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14702</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -2053,6 +2214,11 @@
       <c r="N27" s="8" t="n">
         <v>45822</v>
       </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09884</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -2117,6 +2283,11 @@
       <c r="N28" s="8" t="n">
         <v>45810</v>
       </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10478</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -2181,6 +2352,11 @@
       <c r="N29" s="8" t="n">
         <v>45828</v>
       </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14306</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -2245,6 +2421,11 @@
       <c r="N30" s="8" t="n">
         <v>45809</v>
       </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13580</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -2309,6 +2490,11 @@
       <c r="N31" s="8" t="n">
         <v>45825</v>
       </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06650</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -2373,6 +2559,11 @@
       <c r="N32" s="8" t="n">
         <v>45840</v>
       </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09620</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -2437,6 +2628,11 @@
       <c r="N33" s="8" t="n">
         <v>45816</v>
       </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01365</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -2501,6 +2697,11 @@
       <c r="N34" s="8" t="n">
         <v>45827</v>
       </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08168</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -2565,6 +2766,11 @@
       <c r="N35" s="8" t="n">
         <v>45830</v>
       </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05726</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -2629,6 +2835,11 @@
       <c r="N36" s="8" t="n">
         <v>45844</v>
       </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12920</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -2693,6 +2904,11 @@
       <c r="N37" s="8" t="n">
         <v>45834</v>
       </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08960</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -2757,6 +2973,11 @@
       <c r="N38" s="8" t="n">
         <v>45832</v>
       </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13910</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -2821,6 +3042,11 @@
       <c r="N39" s="8" t="n">
         <v>45836</v>
       </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13844</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -2885,6 +3111,11 @@
       <c r="N40" s="8" t="n">
         <v>45866</v>
       </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07442</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -2949,6 +3180,11 @@
       <c r="N41" s="8" t="n">
         <v>45850</v>
       </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14834</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -3013,6 +3249,11 @@
       <c r="N42" s="8" t="n">
         <v>45869</v>
       </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10874</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -3077,6 +3318,11 @@
       <c r="N43" s="8" t="n">
         <v>45855</v>
       </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11468</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -3141,6 +3387,11 @@
       <c r="N44" s="8" t="n">
         <v>45850</v>
       </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01511</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -3205,6 +3456,11 @@
       <c r="N45" s="8" t="n">
         <v>45867</v>
       </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05396</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -3269,6 +3525,11 @@
       <c r="N46" s="8" t="n">
         <v>45855</v>
       </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11798</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
@@ -3333,6 +3594,11 @@
       <c r="N47" s="8" t="n">
         <v>45875</v>
       </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11600</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -3397,6 +3663,11 @@
       <c r="N48" s="8" t="n">
         <v>45858</v>
       </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10280</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -3461,6 +3732,11 @@
       <c r="N49" s="8" t="n">
         <v>45872</v>
       </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14570</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -3525,6 +3801,11 @@
       <c r="N50" s="8" t="n">
         <v>45865</v>
       </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01584</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -3589,6 +3870,11 @@
       <c r="N51" s="8" t="n">
         <v>45888</v>
       </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09422</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -3653,6 +3939,11 @@
       <c r="N52" s="8" t="n">
         <v>45875</v>
       </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07574</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -3717,6 +4008,11 @@
       <c r="N53" s="8" t="n">
         <v>45867</v>
       </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10544</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -3781,6 +4077,11 @@
       <c r="N54" s="8" t="n">
         <v>45870</v>
       </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01657</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -3845,6 +4146,11 @@
       <c r="N55" s="8" t="n">
         <v>45890</v>
       </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05528</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -3909,6 +4215,11 @@
       <c r="N56" s="8" t="n">
         <v>45886</v>
       </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14372</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -3973,6 +4284,11 @@
       <c r="N57" s="8" t="n">
         <v>45880</v>
       </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05132</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -4037,6 +4353,11 @@
       <c r="N58" s="8" t="n">
         <v>45905</v>
       </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07244</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -4101,6 +4422,11 @@
       <c r="N59" s="8" t="n">
         <v>45898</v>
       </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07706</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -4165,6 +4491,11 @@
       <c r="N60" s="8" t="n">
         <v>45908</v>
       </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07838</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -4229,6 +4560,11 @@
       <c r="N61" s="8" t="n">
         <v>45919</v>
       </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12590</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -4293,6 +4629,11 @@
       <c r="N62" s="8" t="n">
         <v>45889</v>
       </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01730</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -4357,6 +4698,11 @@
       <c r="N63" s="8" t="n">
         <v>45909</v>
       </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05858</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -4421,6 +4767,11 @@
       <c r="N64" s="8" t="n">
         <v>45914</v>
       </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14768</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -4485,6 +4836,11 @@
       <c r="N65" s="8" t="n">
         <v>45903</v>
       </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12458</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -4549,6 +4905,11 @@
       <c r="N66" s="8" t="n">
         <v>45932</v>
       </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13382</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -4613,6 +4974,11 @@
       <c r="N67" s="8" t="n">
         <v>45930</v>
       </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14174</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -4677,6 +5043,11 @@
       <c r="N68" s="8" t="n">
         <v>45910</v>
       </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10676</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -4741,6 +5112,11 @@
       <c r="N69" s="8" t="n">
         <v>45910</v>
       </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05198</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -4805,6 +5181,11 @@
       <c r="N70" s="8" t="n">
         <v>45897</v>
       </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09752</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -4869,6 +5250,11 @@
       <c r="N71" s="8" t="n">
         <v>45915</v>
       </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09224</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
@@ -4933,6 +5319,11 @@
       <c r="N72" s="8" t="n">
         <v>45909</v>
       </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08498</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
@@ -4997,6 +5388,11 @@
       <c r="N73" s="8" t="n">
         <v>45903</v>
       </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06914</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
@@ -5061,6 +5457,11 @@
       <c r="N74" s="8" t="n">
         <v>45912</v>
       </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11534</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
@@ -5125,6 +5526,11 @@
       <c r="N75" s="8" t="n">
         <v>45909</v>
       </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01803</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
@@ -5189,6 +5595,11 @@
       <c r="N76" s="8" t="n">
         <v>45928</v>
       </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09290</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
@@ -5253,6 +5664,11 @@
       <c r="N77" s="8" t="n">
         <v>45929</v>
       </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05066</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
@@ -5317,6 +5733,11 @@
       <c r="N78" s="8" t="n">
         <v>45931</v>
       </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12326</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
@@ -5381,6 +5802,11 @@
       <c r="N79" s="8" t="n">
         <v>45932</v>
       </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07376</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
@@ -5445,6 +5871,11 @@
       <c r="N80" s="8" t="n">
         <v>45928</v>
       </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01876</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
@@ -5509,6 +5940,11 @@
       <c r="N81" s="8" t="n">
         <v>45926</v>
       </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12194</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
@@ -5573,6 +6009,11 @@
       <c r="N82" s="8" t="n">
         <v>45946</v>
       </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13646</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
@@ -5637,6 +6078,11 @@
       <c r="N83" s="8" t="n">
         <v>45963</v>
       </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11996</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
@@ -5701,6 +6147,11 @@
       <c r="N84" s="8" t="n">
         <v>45938</v>
       </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-01949</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
@@ -5765,6 +6216,11 @@
       <c r="N85" s="8" t="n">
         <v>45956</v>
       </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07310</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
@@ -5829,6 +6285,11 @@
       <c r="N86" s="8" t="n">
         <v>45935</v>
       </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13052</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
@@ -5893,6 +6354,11 @@
       <c r="N87" s="8" t="n">
         <v>45965</v>
       </c>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11006</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
@@ -5957,6 +6423,11 @@
       <c r="N88" s="8" t="n">
         <v>45962</v>
       </c>
+      <c r="O88" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12524</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
@@ -6021,6 +6492,11 @@
       <c r="N89" s="8" t="n">
         <v>45971</v>
       </c>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12986</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
@@ -6085,6 +6561,11 @@
       <c r="N90" s="8" t="n">
         <v>45979</v>
       </c>
+      <c r="O90" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09158</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
@@ -6149,6 +6630,11 @@
       <c r="N91" s="8" t="n">
         <v>45968</v>
       </c>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09356</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
@@ -6213,6 +6699,11 @@
       <c r="N92" s="8" t="n">
         <v>45963</v>
       </c>
+      <c r="O92" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05990</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
@@ -6277,6 +6768,11 @@
       <c r="N93" s="8" t="n">
         <v>45969</v>
       </c>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11732</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
@@ -6341,6 +6837,11 @@
       <c r="N94" s="8" t="n">
         <v>45968</v>
       </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06848</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
@@ -6405,6 +6906,11 @@
       <c r="N95" s="8" t="n">
         <v>45957</v>
       </c>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07046</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
@@ -6469,6 +6975,11 @@
       <c r="N96" s="8" t="n">
         <v>45962</v>
       </c>
+      <c r="O96" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12656</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
@@ -6533,6 +7044,11 @@
       <c r="N97" s="8" t="n">
         <v>45974</v>
       </c>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10610</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
@@ -6597,6 +7113,11 @@
       <c r="N98" s="8" t="n">
         <v>45970</v>
       </c>
+      <c r="O98" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10148</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
@@ -6661,6 +7182,11 @@
       <c r="N99" s="8" t="n">
         <v>45956</v>
       </c>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02022</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -6725,6 +7251,11 @@
       <c r="N100" s="8" t="n">
         <v>45957</v>
       </c>
+      <c r="O100" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13250</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
@@ -6789,6 +7320,11 @@
       <c r="N101" s="8" t="n">
         <v>45963</v>
       </c>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02095</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
@@ -6853,6 +7389,11 @@
       <c r="N102" s="8" t="n">
         <v>45964</v>
       </c>
+      <c r="O102" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08366</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
@@ -6917,6 +7458,11 @@
       <c r="N103" s="8" t="n">
         <v>45967</v>
       </c>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09026</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
@@ -6981,6 +7527,11 @@
       <c r="N104" s="8" t="n">
         <v>45996</v>
       </c>
+      <c r="O104" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06452</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
@@ -7045,6 +7596,11 @@
       <c r="N105" s="8" t="n">
         <v>45998</v>
       </c>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09488</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
@@ -7109,6 +7665,11 @@
       <c r="N106" s="8" t="n">
         <v>45990</v>
       </c>
+      <c r="O106" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11336</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
@@ -7173,6 +7734,11 @@
       <c r="N107" s="8" t="n">
         <v>45999</v>
       </c>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05792</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
@@ -7237,6 +7803,11 @@
       <c r="N108" s="8" t="n">
         <v>45974</v>
       </c>
+      <c r="O108" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08234</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
@@ -7301,6 +7872,11 @@
       <c r="N109" s="8" t="n">
         <v>46010</v>
       </c>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07508</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
@@ -7365,6 +7941,11 @@
       <c r="N110" s="8" t="n">
         <v>46003</v>
       </c>
+      <c r="O110" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06716</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
@@ -7429,6 +8010,11 @@
       <c r="N111" s="8" t="n">
         <v>45994</v>
       </c>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14636</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -7493,6 +8079,11 @@
       <c r="N112" s="8" t="n">
         <v>46004</v>
       </c>
+      <c r="O112" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06386</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
@@ -7557,6 +8148,11 @@
       <c r="N113" s="8" t="n">
         <v>46005</v>
       </c>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05924</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
@@ -7621,6 +8217,11 @@
       <c r="N114" s="8" t="n">
         <v>45982</v>
       </c>
+      <c r="O114" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08036</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -7685,6 +8286,11 @@
       <c r="N115" s="8" t="n">
         <v>45996</v>
       </c>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10940</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -7749,6 +8355,11 @@
       <c r="N116" s="8" t="n">
         <v>46003</v>
       </c>
+      <c r="O116" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06122</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -7813,6 +8424,11 @@
       <c r="N117" s="8" t="n">
         <v>46001</v>
       </c>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14438</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -7877,6 +8493,11 @@
       <c r="N118" s="8" t="n">
         <v>45988</v>
       </c>
+      <c r="O118" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09092</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
@@ -7941,6 +8562,11 @@
       <c r="N119" s="8" t="n">
         <v>46025</v>
       </c>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10082</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -8005,6 +8631,11 @@
       <c r="N120" s="8" t="n">
         <v>45989</v>
       </c>
+      <c r="O120" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10412</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
@@ -8069,6 +8700,11 @@
       <c r="N121" s="8" t="n">
         <v>45994</v>
       </c>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14108</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
@@ -8133,6 +8769,11 @@
       <c r="N122" s="8" t="n">
         <v>45996</v>
       </c>
+      <c r="O122" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02168</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
@@ -8197,6 +8838,11 @@
       <c r="N123" s="8" t="n">
         <v>45998</v>
       </c>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11204</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
@@ -8261,6 +8907,11 @@
       <c r="N124" s="8" t="n">
         <v>46015</v>
       </c>
+      <c r="O124" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09950</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
@@ -8325,6 +8976,11 @@
       <c r="N125" s="8" t="n">
         <v>46017</v>
       </c>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09686</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
@@ -8389,6 +9045,11 @@
       <c r="N126" s="8" t="n">
         <v>46013</v>
       </c>
+      <c r="O126" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10214</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
@@ -8453,6 +9114,11 @@
       <c r="N127" s="8" t="n">
         <v>46016</v>
       </c>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08564</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
@@ -8517,6 +9183,11 @@
       <c r="N128" s="8" t="n">
         <v>46014</v>
       </c>
+      <c r="O128" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11864</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
@@ -8581,6 +9252,11 @@
       <c r="N129" s="8" t="n">
         <v>46006</v>
       </c>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14042</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
@@ -8645,6 +9321,11 @@
       <c r="N130" s="8" t="n">
         <v>46021</v>
       </c>
+      <c r="O130" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08432</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
@@ -8709,6 +9390,11 @@
       <c r="N131" s="8" t="n">
         <v>46018</v>
       </c>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02314</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
@@ -8773,6 +9459,11 @@
       <c r="N132" s="8" t="n">
         <v>46022</v>
       </c>
+      <c r="O132" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06188</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
@@ -8837,6 +9528,11 @@
       <c r="N133" s="8" t="n">
         <v>46029</v>
       </c>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13316</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
@@ -8901,6 +9597,11 @@
       <c r="N134" s="8" t="n">
         <v>46020</v>
       </c>
+      <c r="O134" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13514</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
@@ -8965,6 +9666,11 @@
       <c r="N135" s="8" t="n">
         <v>46036</v>
       </c>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06584</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
@@ -9029,6 +9735,11 @@
       <c r="N136" s="8" t="n">
         <v>46051</v>
       </c>
+      <c r="O136" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10346</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
@@ -9093,6 +9804,11 @@
       <c r="N137" s="8" t="n">
         <v>46022</v>
       </c>
+      <c r="O137" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13712</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
@@ -9157,6 +9873,11 @@
       <c r="N138" s="8" t="n">
         <v>46033</v>
       </c>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07112</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
@@ -9221,6 +9942,11 @@
       <c r="N139" s="8" t="n">
         <v>46059</v>
       </c>
+      <c r="O139" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12128</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
@@ -9285,6 +10011,11 @@
       <c r="N140" s="8" t="n">
         <v>46030</v>
       </c>
+      <c r="O140" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02387</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
@@ -9349,6 +10080,11 @@
       <c r="N141" s="8" t="n">
         <v>46062</v>
       </c>
+      <c r="O141" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12260</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
@@ -9413,6 +10149,11 @@
       <c r="N142" s="8" t="n">
         <v>46054</v>
       </c>
+      <c r="O142" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11270</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
@@ -9477,6 +10218,11 @@
       <c r="N143" s="8" t="n">
         <v>46056</v>
       </c>
+      <c r="O143" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05594</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
@@ -9541,6 +10287,11 @@
       <c r="N144" s="8" t="n">
         <v>46053</v>
       </c>
+      <c r="O144" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11138</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
@@ -9605,6 +10356,11 @@
       <c r="N145" s="8" t="n">
         <v>46056</v>
       </c>
+      <c r="O145" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-07904</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
@@ -9669,6 +10425,11 @@
       <c r="N146" s="8" t="n">
         <v>46061</v>
       </c>
+      <c r="O146" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02241</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
@@ -9733,6 +10494,11 @@
       <c r="N147" s="8" t="n">
         <v>46043</v>
       </c>
+      <c r="O147" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02460</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -9797,6 +10563,11 @@
       <c r="N148" s="8" t="n">
         <v>46063</v>
       </c>
+      <c r="O148" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-09554</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
@@ -9861,6 +10632,11 @@
       <c r="N149" s="8" t="n">
         <v>46071</v>
       </c>
+      <c r="O149" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05660</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
@@ -9925,6 +10701,11 @@
       <c r="N150" s="8" t="n">
         <v>46057</v>
       </c>
+      <c r="O150" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12788</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
@@ -9989,6 +10770,11 @@
       <c r="N151" s="8" t="n">
         <v>46054</v>
       </c>
+      <c r="O151" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06254</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
@@ -10053,6 +10839,11 @@
       <c r="N152" s="8" t="n">
         <v>46054</v>
       </c>
+      <c r="O152" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06782</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
@@ -10117,6 +10908,11 @@
       <c r="N153" s="8" t="n">
         <v>46057</v>
       </c>
+      <c r="O153" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08828</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
@@ -10181,6 +10977,11 @@
       <c r="N154" s="8" t="n">
         <v>46055</v>
       </c>
+      <c r="O154" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02533</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
@@ -10245,70 +11046,29 @@
       <c r="N155" s="8" t="n">
         <v>46083</v>
       </c>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14504</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>ORD-2025-0726</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="n">
-        <v>46048</v>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>通常受注</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>C-10016</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>サンプル顧客M社</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr">
-        <is>
-          <t>井上 大輔</t>
-        </is>
-      </c>
-      <c r="H156" s="6" t="n">
-        <v>1389841</v>
-      </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>○ 限度内</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>不要（自動）</t>
-        </is>
-      </c>
-      <c r="L156" s="5" t="inlineStr">
-        <is>
-          <t>(SAP自動承認)</t>
-        </is>
-      </c>
-      <c r="M156" s="3" t="inlineStr">
-        <is>
-          <t>2026/01/26</t>
-        </is>
-      </c>
-      <c r="N156" s="8" t="n">
-        <v>46089</v>
-      </c>
+      <c r="B156" s="9" t="n"/>
+      <c r="C156" s="9" t="n"/>
+      <c r="D156" s="9" t="n"/>
+      <c r="E156" s="9" t="n"/>
+      <c r="F156" s="9" t="n"/>
+      <c r="G156" s="9" t="n"/>
+      <c r="H156" s="9" t="n"/>
+      <c r="I156" s="9" t="n"/>
+      <c r="J156" s="9" t="n"/>
+      <c r="K156" s="9" t="n"/>
+      <c r="L156" s="9" t="n"/>
+      <c r="M156" s="9" t="n"/>
+      <c r="N156" s="10" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
@@ -10373,6 +11133,11 @@
       <c r="N157" s="8" t="n">
         <v>46076</v>
       </c>
+      <c r="O157" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11666</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
@@ -10437,6 +11202,11 @@
       <c r="N158" s="8" t="n">
         <v>46069</v>
       </c>
+      <c r="O158" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02606</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
@@ -10501,6 +11271,11 @@
       <c r="N159" s="8" t="n">
         <v>46093</v>
       </c>
+      <c r="O159" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-12392</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
@@ -10565,6 +11340,11 @@
       <c r="N160" s="8" t="n">
         <v>46081</v>
       </c>
+      <c r="O160" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11402</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -10629,6 +11409,11 @@
       <c r="N161" s="8" t="n">
         <v>46101</v>
       </c>
+      <c r="O161" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13448</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
@@ -10693,6 +11478,11 @@
       <c r="N162" s="8" t="n">
         <v>46087</v>
       </c>
+      <c r="O162" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02679</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
@@ -10757,6 +11547,11 @@
       <c r="N163" s="8" t="n">
         <v>46103</v>
       </c>
+      <c r="O163" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06056</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -10821,6 +11616,11 @@
       <c r="N164" s="8" t="n">
         <v>46103</v>
       </c>
+      <c r="O164" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13118</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -10885,6 +11685,11 @@
       <c r="N165" s="8" t="n">
         <v>46105</v>
       </c>
+      <c r="O165" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-11072</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -10949,6 +11754,11 @@
       <c r="N166" s="8" t="n">
         <v>46096</v>
       </c>
+      <c r="O166" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02752</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -11013,6 +11823,11 @@
       <c r="N167" s="8" t="n">
         <v>46101</v>
       </c>
+      <c r="O167" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14240</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
@@ -11077,6 +11892,11 @@
       <c r="N168" s="8" t="n">
         <v>46121</v>
       </c>
+      <c r="O168" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-05330</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -11141,6 +11961,11 @@
       <c r="N169" s="8" t="n">
         <v>46130</v>
       </c>
+      <c r="O169" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-06980</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -11205,6 +12030,11 @@
       <c r="N170" s="8" t="n">
         <v>46140</v>
       </c>
+      <c r="O170" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08300</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -11269,6 +12099,11 @@
       <c r="N171" s="8" t="n">
         <v>46137</v>
       </c>
+      <c r="O171" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13976</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
@@ -11333,6 +12168,11 @@
       <c r="N172" s="8" t="n">
         <v>46107</v>
       </c>
+      <c r="O172" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08696</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
@@ -11397,6 +12237,11 @@
       <c r="N173" s="8" t="n">
         <v>46128</v>
       </c>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-14900</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
@@ -11461,6 +12306,11 @@
       <c r="N174" s="8" t="n">
         <v>46144</v>
       </c>
+      <c r="O174" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-10742</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
@@ -11525,6 +12375,11 @@
       <c r="N175" s="8" t="n">
         <v>46119</v>
       </c>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-13184</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
@@ -11589,6 +12444,11 @@
       <c r="N176" s="8" t="n">
         <v>46119</v>
       </c>
+      <c r="O176" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-02825</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
@@ -11652,6 +12512,11 @@
       </c>
       <c r="N177" s="8" t="n">
         <v>46138</v>
+      </c>
+      <c r="O177" s="3" t="inlineStr">
+        <is>
+          <t>CUST-PO-2025-08102</t>
+        </is>
       </c>
     </row>
   </sheetData>
